--- a/extenbooks/S505.xlsx
+++ b/extenbooks/S505.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>derived, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S505-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S505-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S505-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>149.94</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>149.94</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>148.64</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>148.64</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>165.26</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>165.26</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>188.25</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>188.25</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>194.51</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>194.51</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>204.52</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>204.52</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>208.2</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>228.55</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>228.55</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>236.97</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>236.97</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>250.25</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>250.25</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>256.15</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>278.42</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>278.42</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>286.46</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>286.46</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>296.54</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>296.54</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>320.2</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>320.2</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>337.71</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>364.54</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>395</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>430.65</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>430.65</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>454.4</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>454.4</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>493.63</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>493.63</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>523.83</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>523.83</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>547.67</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>547.67</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>596.7</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>596.7</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>645.98</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>645.98</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>719.75</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>719.75</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>778.25</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>778.25</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>867.02</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>867.02</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>968.8200000000001</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>968.8200000000001</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>1083.13</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>1083.13</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>1221.07</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>1221.07</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>1346.24</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>1346.24</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>1462.7</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>1462.7</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>1668.19</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>1668.19</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>1724.68</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>1724.68</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>1865.8</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>1865.8</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>2101.78</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>2101.78</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>2258.68</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>2258.68</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>2401.11</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>2401.11</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>2563.38</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>2563.38</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>2752.81</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>2752.81</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,390 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>2943.35</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2943.35</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2005.871409</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2005.871409</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2081.58940259172</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2081.58940259172</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2192.977680808293</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>2192.977680808293</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2181.823856632222</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2181.823856632222</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>2229.472479377573</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2229.472479377573</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2435.321232819287</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>2435.321232819287</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2679.218315568949</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2679.218315568949</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2920.440952223643</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2920.440952223643</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3158.700019999654</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>3158.700019999654</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>3268.279501734998</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3268.279501734998</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3270.930917784019</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>3270.930917784019</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>3091.420931655564</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>3091.420931655564</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3333.959293337008</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3333.959293337008</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3510.697296232865</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>3510.697296232865</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3619.083231833341</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3619.083231833341</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3842.810214901529</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>3842.810214901529</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>3969.476807734097</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>3969.476807734097</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>3993.275855486784</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>3993.275855486784</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>3980.701817584627</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>3980.701817584627</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4187.974471379384</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>4187.974471379384</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>4429.737761947764</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>4429.737761947764</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>4517.026579541825</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>4517.026579541825</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>4356.540069469879</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>4356.540069469879</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>5191.28848681666</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>5191.28848681666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5964.846767810163</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>5964.846767810163</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6209.559709495015</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>6209.559709495015</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>6325.074392770684</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>6325.074392770684</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_4, Fig_9_1</t>
+          <t>Fig_5_4, Fig_9_1, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,386 +1642,391 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S505-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S505-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S505-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S505 — Surplus Value (S* = VA* - V*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t># S505 — Surplus Value (S* = VA* - V*)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Surplus Value: S* = VA* - V*. Identity-checked against VA_star and V_star in H.1.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Surplus Value: S* = VA* - V*. Identity-checked against VA_star and V_star in H.1.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S505-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S505-EXT` | derived | 1990-2024 | billions_dollars |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>| `S505-COMBINED` |  | 1948-2024 | billions_dollars |</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>| `S505-A` | S&amp;T 1994 | 1948-1989 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S505-EXT` | derived | 1990-2024 | billions_dollars |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>| `S505-COMBINED` |  | 1948-2024 | billions_dollars |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>### S505-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2. Extract column `S_star` (and the `year` index).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>### S505-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `S_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1948=149.94, 1972=645.98, 1989=2943.35</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S505_surplus_value.py` writes to `data/intermediate/validation/S505.json`.</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1948=149.94, 1972=645.98, 1989=2943.35</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tolerance class: `dollar_series` (rel 0.01 / abs 1.0).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S505_surplus_value.py` writes to `data/intermediate/validation/S505.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S505_surplus_value.py</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S505.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S505_surplus_value.py</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S505.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2034,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S505_surplus_value.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -1385,65 +2042,105 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S505_surplus_value.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S505.csv</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S505_surplus_value.py</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S505.csv</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S505_surplus_value.py</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1460,10 +2157,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1488,250 +2185,400 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S* = GFP - V* (equivalently S* = TP* - C*_m - V*). Surplus value is the portion of new value created in production that is not paid to productive workers. It is the source of profit, rent, interest, taxes, and unproductive wages in the Marxian framework.</t>
+          <t>The estimates of variable capital in the previous section allow us to calculate surplus value and surplus product. By definition, S* = VA* − V* = surplus value (in money form); S*/V* = rate of surplus value; NP* = the necessary product (consumption of productive workers) = V*; SP* = FP* − NP* = surplus product.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+          <t>ST_1994, Ch5, p.113-114; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived from S503 (GFP) minus S504 (V*). Book period from Table 5.5. Extension spliced at 1989: for the extended period, S* = GFP_extended - V*_extended, though GFP extension is constrained by S502.</t>
+          <t>P+ is intended as a 'naive' measure of surplus value, as directly derived from NIPA. Since NIPA does not estimate the wage equivalent, the only wage cost directly shown would be EC. Hence, P+ = VA−EC = NNP−EC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+          <t>ST_1994, Ch5, p.114, footnote 14; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.4 shows S* as the surplus component of GFP in the full revenue account. Fig 9.1 uses S* in long-run accumulation analysis showing that surplus value growth drives capital accumulation.</t>
+          <t>For U.S. data, the orthodox measure VA = P + EC remains within 10% of the Marxian measure VA* = V* + S*, so the difference between P/EC and S*/V* is largely due to the fact that V* = Wp &lt;&lt; EC. But we cannot assume that the rough equality that holds for the United States between the two value-added measures is a universal phenomenon.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.4, 9.1</t>
+          <t>ST_1994, Ch5, p.114, footnote 15; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theoretical_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Surplus value in the Marxian sense is fundamentally different from profit in orthodox accounts. S* includes not just corporate profits but also the portions of rent, interest, indirect taxes, and unproductive-sector wages that originate as transfers from the surplus created in production.</t>
+          <t>Figure 5.12 compares real surplus value and real profits (defined here as real P). Both rise strongly, but not equally so; real surplus value rises about 16% relative to real profits.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 chunk_23-chunk_24</t>
+          <t>ST_1994, Ch5, p.114; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2013) finds surplus value growing relative to V* over 1964-2010, consistent with ST's findings for 1948-1989. Mohun's exploitation rates are ~2.3-2.5 vs ST's 2.6-2.7, reflecting the broader productive sector classification. See mohun_exploitation_rates*.csv.</t>
+          <t>S* = VA* − V* = surplus value (in money form); S*/V* = rate of surplus value; NP* = the necessary product (consumption of productive workers) = V*; SP* = FP* − NP* = surplus product.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S* extension beyond 1989 is doubly constrained: by S502 (for GFP) and by S504 extension quality. If GFP is approximated via BEA value-added for productive sectors, the resulting S* carries both approximation errors.</t>
+          <t>P⁺ is intended as a 'naive' measure of surplus value, as directly derived from NIPA. Since NIPA does not estimate the wage equivalent, the only wage cost directly shown would be EC. Hence, P⁺ = VA − EC = NNP − EC.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPR T505_DPR.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-010: DIV-001 (K→K* capital stock restriction) is BLOCKED pending a comprehensive unit audit. S505 (S*) is in millions from Table 5.7, while K from BEA Fixed Assets uses a different unit convention (UNIT_MULT=6). Computing S*/K or any ratio involving both series produces inflated results until unit normalization is completed. The S*/K ratio for profit rate purposes must not be computed until the unit mismatch is resolved. ADJ-001 remains BLOCKED.</t>
+          <t>Figure 5.12 compares real surplus value and real profits (defined here as real P). Both rise strongly, but not equally so; real surplus value rises about 16% relative to real profits.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-010 (2026-04-09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S* = GFP - V* (equivalently S* = TP* - C*_m - V*). Surplus value is the portion of new value created in production that is not paid to productive workers. It is the source of profit, rent, interest, taxes, and unproductive wages in the Marxian framework.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/equations/page_310_equations.txt</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.5. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. DEC-010: DIV-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Derived from S503 (GFP) minus S504 (V*). Book period from Table 5.5. Extension spliced at 1989: for the extended period, S* = GFP_extended - V*_extended, though GFP extension is constrained by S502.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Knowledge_Base/tables/page_310_table_E2.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 5.4 shows S* as the surplus component of GFP in the full revenue account. Fig 9.1 uses S* in long-run accumulation analysis showing that surplus value growth drives capital accumulation.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.4, 9.1</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>theoretical_note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Surplus value in the Marxian sense is fundamentally different from profit in orthodox accounts. S* includes not just corporate profits but also the portions of rent, interest, indirect taxes, and unproductive-sector wages that originate as transfers from the surplus created in production.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 chunk_23-chunk_24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Extension constrained by S502 and S504 dependencies</t>
+          <t>Mohun (2013) finds surplus value growing relative to V* over 1964-2010, consistent with ST's findings for 1948-1989. Mohun's exploitation rates are ~2.3-2.5 vs ST's 2.6-2.7, reflecting the broader productive sector classification. See mohun_exploitation_rates*.csv.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mohun's broader productive classification yields lower S*/V* ratio</t>
+          <t>S* extension beyond 1989 is doubly constrained: by S502 (for GFP) and by S504 extension quality. If GFP is approximated via BEA value-added for productive sectors, the resulting S* carries both approximation errors.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DPR T505_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Double approximation error risk in extended period</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DEC-010: DIV-001 BLOCKED — unit mismatch between S505 (millions, Table 5.7) and BEA Fixed Assets K (UNIT_MULT=6) prevents S*/K computation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>[internal-decision-record]: DIV-001 (K→K* capital stock restriction) is BLOCKED pending a comprehensive unit audit. S505 (S*) is in millions from Table 5.7, while K from BEA Fixed Assets uses a different unit convention (UNIT_MULT=6). Computing S*/K or any ratio involving both series produces inflated results until unit normalization is completed. The S*/K ratio for profit rate purposes must not be computed until the unit mismatch is resolved. ADJ-001 remains BLOCKED.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log] [internal-decision-record] (2026-04-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S503</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.5. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. [internal-decision-record]: DIV-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Extension constrained by S502 and S504 dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mohun's broader productive classification yields lower S*/V* ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Double approximation error risk in extended period</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]: DIV-001 BLOCKED — unit mismatch between S505 (millions, Table 5.7) and BEA Fixed Assets K (UNIT_MULT=6) prevents S*/K computation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S503</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
         <is>
           <t>S504</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>S506</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>S507</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
         <is>
           <t>S513</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1748,11 +2595,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1852,91 +2699,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BEA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S503', 'S504']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S505-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S505-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Appendix H.1 column S_star (surplus value, 1948-1989); identity S* = VA* - V*, with VA* = GFP (no taxes on production) or VA* = GFP - T_indirect", "shaikh_appendix_ref": "Appendix H.1 (S_star, 1948-1989); Figures 5.4, 5.6 (aggregate measures); Table 5.7 (rate of surplus value)", "extension_source": "Derived series: S* = S503 - S504 (GFP - V*). Inherits sources from S503 and S504.", "extension_url": "n/a (derived from S503 and S504)", "conceptual_continuity": "Surplus Value S* is the residual of productive value added (GFP) over variable capital (V*) -- the Marxian surplus appropriated by capital. It is a derived identity, not a directly observed series. Conceptual continuity is mechanical: the extension is whatever the extensions of S503 and S504 yield via the identity. The book itself reports S* in Appendix H.1, but the construction is S* = GFP - V*.", "vintage_note": "Inherits all vintage divergences from S503 (and therefore from S501, S502) and S504. No additional vintage issues.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S503", "S504"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 149.94, "1972": 645.98, "1989": 2943.35}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0, 30000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S505.xlsx
+++ b/extenbooks/S505.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1090,380 +1090,492 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2005.871409</v>
+        <v>2994.578224387631</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>2005.871409</v>
+        <v>2994.578224387631</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2081.58940259172</v>
+        <v>2834.316066036517</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2081.58940259172</v>
+        <v>2834.316066036517</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2192.977680808293</v>
+        <v>2676.248113669418</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2192.977680808293</v>
+        <v>2676.248113669418</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2181.823856632222</v>
+        <v>2520.236619680048</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2181.823856632222</v>
+        <v>2520.236619680048</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2229.472479377573</v>
+        <v>2366.145379526969</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2229.472479377573</v>
+        <v>2366.145379526969</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2435.321232819287</v>
+        <v>2213.839612245989</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2435.321232819287</v>
+        <v>2213.839612245989</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2679.218315568949</v>
+        <v>2063.185841975643</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2679.218315568949</v>
+        <v>2063.185841975643</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2920.440952223643</v>
+        <v>1914.051780391237</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2920.440952223643</v>
+        <v>1914.051780391237</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>3158.700019999654</v>
+        <v>2028.691530000001</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>3158.700019999654</v>
+        <v>2028.691530000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3268.279501734998</v>
+        <v>2105.674058893246</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>3268.279501734998</v>
+        <v>2105.674058893246</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>3270.930917784019</v>
+        <v>2218.648417698317</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3270.930917784019</v>
+        <v>2218.648417698317</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3091.420931655564</v>
+        <v>2207.375633299374</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3091.420931655564</v>
+        <v>2207.375633299374</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3333.959293337008</v>
+        <v>2254.396810653945</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>3333.959293337008</v>
+        <v>2254.396810653945</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3510.697296232865</v>
+        <v>2460.443468976761</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3510.697296232865</v>
+        <v>2460.443468976761</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>3619.083231833341</v>
+        <v>2705.511015349668</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>3619.083231833341</v>
+        <v>2705.511015349668</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3842.810214901529</v>
+        <v>2947.853051488098</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>3842.810214901529</v>
+        <v>2947.853051488098</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3969.476807734097</v>
+        <v>3187.550723943321</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>3969.476807734097</v>
+        <v>3187.550723943321</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3993.275855486784</v>
+        <v>3298.210776358449</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>3993.275855486784</v>
+        <v>3298.210776358449</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>3980.701817584627</v>
+        <v>3300.788228801146</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>3980.701817584627</v>
+        <v>3300.788228801146</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>4187.974471379384</v>
+        <v>3118.196693181543</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>4187.974471379384</v>
+        <v>3118.196693181543</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>4429.737761947764</v>
+        <v>3360.661275120993</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>4429.737761947764</v>
+        <v>3360.661275120993</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>4517.026579541825</v>
+        <v>3538.51282727184</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>4517.026579541825</v>
+        <v>3538.51282727184</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>4356.540069469879</v>
+        <v>3648.270791948364</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>4356.540069469879</v>
+        <v>3648.270791948364</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>5191.28848681666</v>
+        <v>3872.863592156437</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>5191.28848681666</v>
+        <v>3872.863592156437</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>5964.846767810163</v>
+        <v>4001.195444244884</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>5964.846767810163</v>
+        <v>4001.195444244884</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>6209.559709495015</v>
+        <v>4026.398730761618</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>6209.559709495015</v>
+        <v>4026.398730761618</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>4014.40742578766</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>4014.40742578766</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>4223.329760514885</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>4223.329760514885</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>4467.134413187936</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>4467.134413187936</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4556.167050252503</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4556.167050252503</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4395.259223421008</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4395.259223421008</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>5232.533719396706</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>5232.533719396706</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>6009.519348545231</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>6009.519348545231</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>6256.743375558464</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>6256.743375558464</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>6325.074392770684</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>6325.074392770684</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>6374.819823858421</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>6374.819823858421</v>
       </c>
     </row>
   </sheetData>
@@ -2326,7 +2438,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Derived from S503 (GFP) minus S504 (V*). Book period from Table 5.5. Extension spliced at 1989: for the extended period, S* = GFP_extended - V*_extended, though GFP extension is constrained by S502.</t>
+          <t>Derived from S503 (GFP) minus S504 (V*). Book period from Table 5.6 ('Total wages and variable capital, 1948-89', p.115; corrected 2026-06-11 from the erroneous 'Table 5.5', which is 'Total wages and productive employment'). Extension spliced at 1989: for the extended period, S* = GFP_extended - V*_extended, though GFP extension is constrained by S502.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2460,7 +2572,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.5. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. [internal-decision-record]: DIV-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
+          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.6. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. [internal-decision-record]: DIV-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
         </is>
       </c>
     </row>
@@ -2595,10 +2707,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2874,6 +2986,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S505.xlsx
+++ b/extenbooks/S505.xlsx
@@ -1096,10 +1096,10 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2994.578224387631</v>
+        <v>1722.209</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>2994.578224387631</v>
+        <v>1722.209</v>
       </c>
     </row>
     <row r="46">
@@ -1110,10 +1110,10 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2834.316066036517</v>
+        <v>1736.369</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2834.316066036517</v>
+        <v>1736.369</v>
       </c>
     </row>
     <row r="47">
@@ -1124,10 +1124,10 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2676.248113669418</v>
+        <v>1813.234</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2676.248113669418</v>
+        <v>1813.234</v>
       </c>
     </row>
     <row r="48">
@@ -1138,10 +1138,10 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2520.236619680048</v>
+        <v>1903.294</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2520.236619680048</v>
+        <v>1903.294</v>
       </c>
     </row>
     <row r="49">
@@ -1152,10 +1152,10 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2366.145379526969</v>
+        <v>2083.021</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2366.145379526969</v>
+        <v>2083.021</v>
       </c>
     </row>
     <row r="50">
@@ -1166,10 +1166,10 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2213.839612245989</v>
+        <v>2190.145</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2213.839612245989</v>
+        <v>2190.145</v>
       </c>
     </row>
     <row r="51">
@@ -1180,10 +1180,10 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>2063.185841975643</v>
+        <v>2352.58</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2063.185841975643</v>
+        <v>2352.58</v>
       </c>
     </row>
     <row r="52">
@@ -1194,10 +1194,10 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1914.051780391237</v>
+        <v>1985.757</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1914.051780391237</v>
+        <v>1985.757</v>
       </c>
     </row>
     <row r="53">
@@ -1208,10 +1208,10 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2028.691530000001</v>
+        <v>2260.847</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>2028.691530000001</v>
+        <v>2260.847</v>
       </c>
     </row>
     <row r="54">
@@ -1222,10 +1222,10 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2105.674058893246</v>
+        <v>2350.694</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2105.674058893246</v>
+        <v>2350.694</v>
       </c>
     </row>
     <row r="55">
@@ -1236,10 +1236,10 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2218.648417698317</v>
+        <v>2479.804</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2218.648417698317</v>
+        <v>2479.804</v>
       </c>
     </row>
     <row r="56">
@@ -1250,10 +1250,10 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2207.375633299374</v>
+        <v>2467.321</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2207.375633299374</v>
+        <v>2467.321</v>
       </c>
     </row>
     <row r="57">
@@ -1264,10 +1264,10 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>2254.396810653945</v>
+        <v>2507.959</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2254.396810653945</v>
+        <v>2507.959</v>
       </c>
     </row>
     <row r="58">
@@ -1278,10 +1278,10 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>2460.443468976761</v>
+        <v>2716.019</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2460.443468976761</v>
+        <v>2716.019</v>
       </c>
     </row>
     <row r="59">
@@ -1292,10 +1292,10 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2705.511015349668</v>
+        <v>2972.994000000001</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2705.511015349668</v>
+        <v>2972.994000000001</v>
       </c>
     </row>
     <row r="60">
@@ -1306,10 +1306,10 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>2947.853051488098</v>
+        <v>3226.724</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2947.853051488098</v>
+        <v>3226.724</v>
       </c>
     </row>
     <row r="61">
@@ -1320,10 +1320,10 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3187.550723943321</v>
+        <v>3481.057000000001</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>3187.550723943321</v>
+        <v>3481.057000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1334,10 +1334,10 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3298.210776358449</v>
+        <v>3602.71</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>3298.210776358449</v>
+        <v>3602.71</v>
       </c>
     </row>
     <row r="63">
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>3300.788228801146</v>
+        <v>3604.535</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>3300.788228801146</v>
+        <v>3604.535</v>
       </c>
     </row>
     <row r="64">
@@ -1362,10 +1362,10 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>3118.196693181543</v>
+        <v>3390.594</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>3118.196693181543</v>
+        <v>3390.594</v>
       </c>
     </row>
     <row r="65">
@@ -1376,10 +1376,10 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3360.661275120993</v>
+        <v>3632.308000000001</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>3360.661275120993</v>
+        <v>3632.308000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1390,10 +1390,10 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>3538.51282727184</v>
+        <v>3821.488</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>3538.51282727184</v>
+        <v>3821.488</v>
       </c>
     </row>
     <row r="67">
@@ -1404,10 +1404,10 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>3648.270791948364</v>
+        <v>3945.204000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>3648.270791948364</v>
+        <v>3945.204000000001</v>
       </c>
     </row>
     <row r="68">
@@ -1418,10 +1418,10 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>3872.863592156437</v>
+        <v>4178.605</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>3872.863592156437</v>
+        <v>4178.605</v>
       </c>
     </row>
     <row r="69">
@@ -1432,10 +1432,10 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>4001.195444244884</v>
+        <v>4323.878000000001</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>4001.195444244884</v>
+        <v>4323.878000000001</v>
       </c>
     </row>
     <row r="70">
@@ -1446,10 +1446,10 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>4026.398730761618</v>
+        <v>4363.367</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>4026.398730761618</v>
+        <v>4363.367</v>
       </c>
     </row>
     <row r="71">
@@ -1460,10 +1460,10 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>4014.40742578766</v>
+        <v>4357.304</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>4014.40742578766</v>
+        <v>4357.304</v>
       </c>
     </row>
     <row r="72">
@@ -1474,10 +1474,10 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>4223.329760514885</v>
+        <v>4583.009</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>4223.329760514885</v>
+        <v>4583.009</v>
       </c>
     </row>
     <row r="73">
@@ -1488,10 +1488,10 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>4467.134413187936</v>
+        <v>4847.581</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>4467.134413187936</v>
+        <v>4847.581</v>
       </c>
     </row>
     <row r="74">
@@ -1502,10 +1502,10 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>4556.167050252503</v>
+        <v>4954.353999999999</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>4556.167050252503</v>
+        <v>4954.353999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4395.259223421008</v>
+        <v>4789.16</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>4395.259223421008</v>
+        <v>4789.16</v>
       </c>
     </row>
     <row r="76">
@@ -1530,10 +1530,10 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>5232.533719396706</v>
+        <v>5652.133000000001</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>5232.533719396706</v>
+        <v>5652.133000000001</v>
       </c>
     </row>
     <row r="77">
@@ -1544,10 +1544,10 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>6009.519348545231</v>
+        <v>6463.986000000001</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>6009.519348545231</v>
+        <v>6463.986000000001</v>
       </c>
     </row>
     <row r="78">
@@ -1558,10 +1558,10 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>6256.743375558464</v>
+        <v>6736.756</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>6256.743375558464</v>
+        <v>6736.756</v>
       </c>
     </row>
     <row r="79">
@@ -1572,10 +1572,10 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>6374.819823858421</v>
+        <v>6880.894</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>6374.819823858421</v>
+        <v>6880.894</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[internal-decision-record]: DIV-001 (K→K* capital stock restriction) is BLOCKED pending a comprehensive unit audit. S505 (S*) is in millions from Table 5.7, while K from BEA Fixed Assets uses a different unit convention (UNIT_MULT=6). Computing S*/K or any ratio involving both series produces inflated results until unit normalization is completed. The S*/K ratio for profit rate purposes must not be computed until the unit mismatch is resolved. ADJ-001 remains BLOCKED.</t>
+          <t>[internal-decision-record]: ADR-S505-001 (K→K* capital stock restriction) is BLOCKED pending a comprehensive unit audit. S505 (S*) is in millions from Table 5.7, while K from BEA Fixed Assets uses a different unit convention (UNIT_MULT=6). Computing S*/K or any ratio involving both series produces inflated results until unit normalization is completed. The S*/K ratio for profit rate purposes must not be computed until the unit mismatch is resolved. ADJ-001 remains BLOCKED.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.6. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. [internal-decision-record]: DIV-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
+          <t>Surplus value is derived as S* = GFP - V*. Book data from Table 5.6. Extension constrained by GFP and V* availability. Mohun provides comparison estimates. [internal-decision-record]: ADR-S505-001 blocked by unit mismatch — S*/K ratios must not be computed until unit normalization is complete.</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[internal-decision-record]: DIV-001 BLOCKED — unit mismatch between S505 (millions, Table 5.7) and BEA Fixed Assets K (UNIT_MULT=6) prevents S*/K computation</t>
+          <t>[internal-decision-record]: ADR-S505-001 BLOCKED — unit mismatch between S505 (millions, Table 5.7) and BEA Fixed Assets K (UNIT_MULT=6) prevents S*/K computation</t>
         </is>
       </c>
     </row>
